--- a/Data/EXCEL/Transfer/dividend/20260225_0_4/6204-dividend-20260225_0_4.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260225_0_4/6204-dividend-20260225_0_4.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260225_0_4\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\20260225_0_4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DBE365CD-3ED9-41F2-8B98-7400126572A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{7F87F904-76EF-40C3-B7F9-DFCB5C2E5418}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4140" yWindow="576" windowWidth="16656" windowHeight="10992" xr2:uid="{0C18AFFA-C8DC-4CA2-BB2E-20F8F3D60F2D}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="22845" windowHeight="19530" xr2:uid="{90197303-D960-4715-B99F-1025C38D46BB}"/>
   </bookViews>
   <sheets>
     <sheet name="6204-dividend-20260225_0_4" sheetId="1" r:id="rId1"/>
@@ -1469,25 +1469,25 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4BA891E7-9A9C-40F2-964D-D156F82551A2}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CA0E0C66-3459-4009-992B-542174BE77ED}">
   <dimension ref="A1:R38"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.109375" customWidth="1"/>
-    <col min="2" max="2" width="7.33203125" customWidth="1"/>
-    <col min="3" max="3" width="8.6640625" customWidth="1"/>
-    <col min="4" max="4" width="8.33203125" customWidth="1"/>
-    <col min="5" max="5" width="8" customWidth="1"/>
-    <col min="6" max="6" width="8.33203125" customWidth="1"/>
-    <col min="7" max="9" width="8" customWidth="1"/>
-    <col min="10" max="10" width="8.33203125" customWidth="1"/>
-    <col min="11" max="13" width="8" customWidth="1"/>
-    <col min="14" max="14" width="8.33203125" customWidth="1"/>
-    <col min="15" max="17" width="8" customWidth="1"/>
-    <col min="18" max="18" width="8.88671875" customWidth="1"/>
+    <col min="1" max="1" width="6.5" customWidth="1"/>
+    <col min="2" max="2" width="9.25" customWidth="1"/>
+    <col min="3" max="3" width="10.75" customWidth="1"/>
+    <col min="4" max="4" width="10.5" customWidth="1"/>
+    <col min="5" max="5" width="10" customWidth="1"/>
+    <col min="6" max="6" width="10.5" customWidth="1"/>
+    <col min="7" max="9" width="10" customWidth="1"/>
+    <col min="10" max="10" width="10.5" customWidth="1"/>
+    <col min="11" max="13" width="10" customWidth="1"/>
+    <col min="14" max="14" width="10.5" customWidth="1"/>
+    <col min="15" max="17" width="10" customWidth="1"/>
+    <col min="18" max="18" width="10.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A1" s="23" t="s">
         <v>0</v>
       </c>
@@ -1515,7 +1515,7 @@
       <c r="Q1" s="32"/>
       <c r="R1" s="24"/>
     </row>
-    <row r="2" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A2" s="25" t="s">
         <v>1</v>
       </c>
@@ -1545,7 +1545,7 @@
       <c r="Q2" s="34"/>
       <c r="R2" s="35"/>
     </row>
-    <row r="3" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A3" s="25" t="s">
         <v>2</v>
       </c>
@@ -1591,7 +1591,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A4" s="27"/>
       <c r="B4" s="28"/>
       <c r="C4" s="7"/>
@@ -1641,7 +1641,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A5" s="39">
         <v>2025</v>
       </c>
@@ -1695,7 +1695,7 @@
         <v>0.47</v>
       </c>
     </row>
-    <row r="6" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A6" s="41">
         <v>2024</v>
       </c>
@@ -1749,7 +1749,7 @@
         <v>0.59</v>
       </c>
     </row>
-    <row r="7" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="15" t="s">
         <v>26</v>
       </c>
@@ -1805,7 +1805,7 @@
         <v>0.59</v>
       </c>
     </row>
-    <row r="8" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A8" s="39">
         <v>2023</v>
       </c>
@@ -1859,7 +1859,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="9" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
         <v>26</v>
       </c>
@@ -1915,7 +1915,7 @@
         <v>23.5</v>
       </c>
     </row>
-    <row r="10" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A10" s="11" t="s">
         <v>26</v>
       </c>
@@ -1971,7 +1971,7 @@
         <v>2.48</v>
       </c>
     </row>
-    <row r="11" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A11" s="41">
         <v>2022</v>
       </c>
@@ -2025,7 +2025,7 @@
         <v>10.9</v>
       </c>
     </row>
-    <row r="12" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A12" s="15" t="s">
         <v>26</v>
       </c>
@@ -2081,7 +2081,7 @@
         <v>3.74</v>
       </c>
     </row>
-    <row r="13" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A13" s="15" t="s">
         <v>26</v>
       </c>
@@ -2137,7 +2137,7 @@
         <v>7.16</v>
       </c>
     </row>
-    <row r="14" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A14" s="39">
         <v>2021</v>
       </c>
@@ -2191,7 +2191,7 @@
         <v>24.7</v>
       </c>
     </row>
-    <row r="15" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
         <v>26</v>
       </c>
@@ -2247,7 +2247,7 @@
         <v>16.3</v>
       </c>
     </row>
-    <row r="16" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A16" s="11" t="s">
         <v>26</v>
       </c>
@@ -2303,7 +2303,7 @@
         <v>8.3699999999999992</v>
       </c>
     </row>
-    <row r="17" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A17" s="41">
         <v>2020</v>
       </c>
@@ -2357,7 +2357,7 @@
         <v>4.83</v>
       </c>
     </row>
-    <row r="18" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A18" s="39">
         <v>2019</v>
       </c>
@@ -2411,7 +2411,7 @@
         <v>4.43</v>
       </c>
     </row>
-    <row r="19" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A19" s="41">
         <v>2018</v>
       </c>
@@ -2465,7 +2465,7 @@
         <v>3.74</v>
       </c>
     </row>
-    <row r="20" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A20" s="39">
         <v>2017</v>
       </c>
@@ -2519,7 +2519,7 @@
         <v>4.3899999999999997</v>
       </c>
     </row>
-    <row r="21" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A21" s="41">
         <v>2016</v>
       </c>
@@ -2573,7 +2573,7 @@
         <v>3.37</v>
       </c>
     </row>
-    <row r="22" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A22" s="39">
         <v>2015</v>
       </c>
@@ -2627,7 +2627,7 @@
         <v>4.33</v>
       </c>
     </row>
-    <row r="23" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A23" s="41">
         <v>2014</v>
       </c>
@@ -2681,7 +2681,7 @@
         <v>4.01</v>
       </c>
     </row>
-    <row r="24" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A24" s="39">
         <v>2013</v>
       </c>
@@ -2735,7 +2735,7 @@
         <v>3.92</v>
       </c>
     </row>
-    <row r="25" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A25" s="41">
         <v>2012</v>
       </c>
@@ -2789,7 +2789,7 @@
         <v>6.18</v>
       </c>
     </row>
-    <row r="26" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A26" s="39">
         <v>2011</v>
       </c>
@@ -2843,7 +2843,7 @@
         <v>7.99</v>
       </c>
     </row>
-    <row r="27" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A27" s="41">
         <v>2010</v>
       </c>
@@ -2897,7 +2897,7 @@
         <v>5.58</v>
       </c>
     </row>
-    <row r="28" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A28" s="39">
         <v>2009</v>
       </c>
@@ -2951,7 +2951,7 @@
         <v>6.94</v>
       </c>
     </row>
-    <row r="29" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A29" s="41">
         <v>2008</v>
       </c>
@@ -3005,7 +3005,7 @@
         <v>9.64</v>
       </c>
     </row>
-    <row r="30" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A30" s="39">
         <v>2007</v>
       </c>
@@ -3059,7 +3059,7 @@
         <v>4.54</v>
       </c>
     </row>
-    <row r="31" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A31" s="41">
         <v>2006</v>
       </c>
@@ -3113,7 +3113,7 @@
         <v>7.07</v>
       </c>
     </row>
-    <row r="32" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A32" s="39">
         <v>2005</v>
       </c>
@@ -3167,7 +3167,7 @@
         <v>7.81</v>
       </c>
     </row>
-    <row r="33" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A33" s="41">
         <v>2004</v>
       </c>
@@ -3221,7 +3221,7 @@
         <v>6.69</v>
       </c>
     </row>
-    <row r="34" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A34" s="39">
         <v>2003</v>
       </c>
@@ -3275,7 +3275,7 @@
         <v>5.77</v>
       </c>
     </row>
-    <row r="35" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A35" s="41">
         <v>2002</v>
       </c>
@@ -3329,7 +3329,7 @@
         <v>4.91</v>
       </c>
     </row>
-    <row r="36" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A36" s="39">
         <v>2001</v>
       </c>
@@ -3383,7 +3383,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="37" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A37" s="41">
         <v>2000</v>
       </c>
@@ -3437,7 +3437,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="38" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A38" s="39" t="s">
         <v>40</v>
       </c>
